--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.627</v>
+        <v>31.614</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24665,7 +24665,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5058.42238</v>
+        <v>5056.34316</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34555,7 +34555,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22219.86512</v>
+        <v>22210.73184</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -1623,7 +1623,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -1725,7 +1725,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -1909,7 +1909,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -2017,7 +2017,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.794</v>
+        <v>31.812</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>244.65</v>
+        <v>243.5</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>44.8</v>
+        <v>44.55</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5085.93206</v>
+        <v>5049.51876</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22340.70544</v>
+        <v>22246.1316</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.812</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5049.51876</v>
+        <v>5030.0949</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22246.1316</v>
+        <v>22160.046</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>243.5</v>
+        <v>244.6</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>44.55</v>
+        <v>45.3</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5030.0949</v>
+        <v>5019.0328</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22160.046</v>
+        <v>22111.312</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.76</v>
+        <v>31.832</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5019.0328</v>
+        <v>5010.67512</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22111.312</v>
+        <v>22067.21568</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.832</v>
+        <v>31.889</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>244.6</v>
+        <v>247.4</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.3</v>
+        <v>45.95</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5010.67512</v>
+        <v>5019.647489999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22067.21568</v>
+        <v>22106.73036</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.889</v>
+        <v>31.857</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5019.647489999999</v>
+        <v>5070.83856</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22106.73036</v>
+        <v>22326.40344</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.857</v>
+        <v>31.808</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>247.4</v>
+        <v>251.2</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.95</v>
+        <v>45.25</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5070.83856</v>
+        <v>5064.62898</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22326.40344</v>
+        <v>22299.06327</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.808</v>
+        <v>31.763</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5064.62898</v>
+        <v>5036.023650000001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22299.06327</v>
+        <v>22290.63814</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.763</v>
+        <v>31.764</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5036.023650000001</v>
+        <v>5036.1822</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22290.63814</v>
+        <v>22291.33992</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.764</v>
+        <v>31.713</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>251.2</v>
+        <v>254.7</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.25</v>
+        <v>45.7</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5036.1822</v>
+        <v>5029.047450000001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22291.33992</v>
+        <v>22259.75982</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.713</v>
+        <v>31.639</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>254.7</v>
+        <v>255.7</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5029.047450000001</v>
+        <v>5090.398709999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22259.75982</v>
+        <v>22551.64642</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.639</v>
+        <v>31.679</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5090.398709999999</v>
+        <v>5107.92196</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22551.64642</v>
+        <v>22580.15762</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.679</v>
+        <v>31.668</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>255.7</v>
+        <v>257</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.4</v>
+        <v>45.05</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5107.92196</v>
+        <v>5106.14832</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22580.15762</v>
+        <v>22572.31704</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.668</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>257</v>
+        <v>256.85</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.05</v>
+        <v>45.15</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5106.14832</v>
+        <v>5061.925300000001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22572.31704</v>
+        <v>22500.66374</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.8</v>
+        <v>31.729</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5061.925300000001</v>
+        <v>5046.49745</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22500.66374</v>
+        <v>22432.08571</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.729</v>
+        <v>31.695</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5046.49745</v>
+        <v>5072.15085</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22432.08571</v>
+        <v>22528.48905</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.695</v>
+        <v>31.776</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5072.15085</v>
+        <v>5085.11328</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22528.48905</v>
+        <v>22586.06304</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.776</v>
+        <v>31.763</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5085.11328</v>
+        <v>5050.63463</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22586.06304</v>
+        <v>22399.2676</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.763</v>
+        <v>31.818</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>256.85</v>
+        <v>255.2</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>45.15</v>
+        <v>43.9</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5050.63463</v>
+        <v>5053.01658</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34575,7 +34575,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22399.2676</v>
+        <v>22387.46298</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -1623,7 +1623,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -1725,7 +1725,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -1909,7 +1909,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -2017,7 +2017,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.837</v>
+        <v>31.826</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5044.572649999999</v>
+        <v>5042.829699999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22364.21902</v>
+        <v>22356.49196</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.826</v>
+        <v>31.906</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>256.3</v>
+        <v>258.25</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>44.25</v>
+        <v>43.65</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5042.829699999999</v>
+        <v>5037.63834</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22356.49196</v>
+        <v>22422.73915</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.906</v>
+        <v>31.812</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>258.25</v>
+        <v>258.3</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>43.65</v>
+        <v>44.05</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5037.63834</v>
+        <v>5019.9336</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22422.73915</v>
+        <v>22343.1582</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.812</v>
+        <v>31.796</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5019.9336</v>
+        <v>5059.69748</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22343.1582</v>
+        <v>22496.94184</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.796</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>258.3</v>
+        <v>265.35</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5059.69748</v>
+        <v>5067.5751</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22496.94184</v>
+        <v>22522.9788</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.71</v>
+        <v>31.719</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>44.05</v>
+        <v>44.8</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5067.5751</v>
+        <v>5078.36898</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22522.9788</v>
+        <v>22593.36576</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.719</v>
+        <v>31.779</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>265.35</v>
+        <v>265.9</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>44.8</v>
+        <v>45.4</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5078.36898</v>
+        <v>5088.13569</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22593.36576</v>
+        <v>22636.81728</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.779</v>
+        <v>31.851</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>265.9</v>
+        <v>265.6</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>45.4</v>
+        <v>44.65</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5088.13569</v>
+        <v>5066.3538342</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22636.81728</v>
+        <v>22673.77137</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.851</v>
+        <v>31.928</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="126" t="n">
-        <v>265.6</v>
+        <v>263.4</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -16410,7 +16410,7 @@
         <v/>
       </c>
       <c r="C3" s="127" t="n">
-        <v>44.65</v>
+        <v>44.05</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(D7:D505)</f>
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5066.3538342</v>
+        <v>5073.999493</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22673.77137</v>
+        <v>22749.32675</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.928</v>
+        <v>31.961</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5073.999493</v>
+        <v>5069.042549999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22749.32675</v>
+        <v>22714.7268</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.961</v>
+        <v>31.921</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24685,7 +24685,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>5069.042549999999</v>
+        <v>5091.718709999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34581,7 +34581,7 @@
         <v/>
       </c>
       <c r="H3" s="116" t="n">
-        <v>22714.7268</v>
+        <v>22789.67874</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -1623,7 +1623,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -1725,7 +1725,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -1909,7 +1909,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW"/>
               </a:p>
@@ -2017,7 +2017,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-TW"/>
         </a:p>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.91</v>
+        <v>31.916</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5100.175300000001</v>
+        <v>5101.13428</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22834.4769</v>
+        <v>22838.77044</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.916</v>
+        <v>31.932</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>263.4</v>
+        <v>263.15</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>44.05</v>
+        <v>45.2</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5101.13428</v>
+        <v>5099.862913200001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22838.77044</v>
+        <v>22862.03472</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>31.932</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5099.862913200001</v>
+        <v>5116.441000000001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22862.03472</v>
+        <v>22939.94014</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.08</v>
+        <v>32.153</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>263.15</v>
+        <v>257.85</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>44.9</v>
+        <v>44.75</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5116.441000000001</v>
+        <v>5123.677009</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22939.94014</v>
+        <v>22987.626585</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.153</v>
+        <v>32.102</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>257.85</v>
+        <v>258.7</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>44.75</v>
+        <v>44.05</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5123.677009</v>
+        <v>5127.33744</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22987.626585</v>
+        <v>22953.6288</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.102</v>
+        <v>32.413</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>258.7</v>
+        <v>250.1</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>44.05</v>
+        <v>45.6</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5127.33744</v>
+        <v>5110.557709999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22953.6288</v>
+        <v>22929.92859</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.413</v>
+        <v>32.349</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5110.557709999999</v>
+        <v>5121.17019</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22929.92859</v>
+        <v>22949.35107</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.349</v>
+        <v>32.385</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>250.1</v>
+        <v>250.35</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>45.6</v>
+        <v>45.75</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5121.17019</v>
+        <v>5126.71104</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22949.35107</v>
+        <v>22974.18112</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.385</v>
+        <v>32.428</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5126.71104</v>
+        <v>5085.35896</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22974.18112</v>
+        <v>22751.80908</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.428</v>
+        <v>32.454</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>250.35</v>
+        <v>247.9</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>45.75</v>
+        <v>45.25</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5085.35896</v>
+        <v>5109.23322</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22751.80908</v>
+        <v>22878.28503</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.454</v>
+        <v>32.666</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>247.9</v>
+        <v>245.3</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>45.25</v>
+        <v>44.25</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5109.23322</v>
+        <v>5131.99815</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22878.28503</v>
+        <v>23015.759</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.666</v>
+        <v>32.379</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>245.3</v>
+        <v>247.6</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>44.25</v>
+        <v>45.4</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5131.99815</v>
+        <v>5109.4062</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>23015.759</v>
+        <v>22885.4772</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.379</v>
+        <v>32.535</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>247.6</v>
+        <v>244.85</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>45.4</v>
+        <v>46.35</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5109.4062</v>
+        <v>5159.88424</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22885.4772</v>
+        <v>23123.98592</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.535</v>
+        <v>32.596</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5159.88424</v>
+        <v>5101.92592</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>23123.98592</v>
+        <v>22892.1708</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.596</v>
+        <v>32.586</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5101.92592</v>
+        <v>5100.36072</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22892.1708</v>
+        <v>22885.1478</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.586</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5100.36072</v>
+        <v>5077.663</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22885.1478</v>
+        <v>22752.7506</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.57</v>
+        <v>32.567</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5077.663</v>
+        <v>5077.1953</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22752.7506</v>
+        <v>22750.65486</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.567</v>
+        <v>32.569</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5077.1953</v>
+        <v>5077.507100000001</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22750.65486</v>
+        <v>22752.05202</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.569</v>
+        <v>32.417</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>244.85</v>
+        <v>244.6</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>46.35</v>
+        <v>46.25</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5077.507100000001</v>
+        <v>5077.798879999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22752.05202</v>
+        <v>22802.44197</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.417</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>244.6</v>
+        <v>249.05</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>46.25</v>
+        <v>46.3</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5077.798879999999</v>
+        <v>5109.156</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22802.44197</v>
+        <v>22923.648</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.4</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5109.156</v>
+        <v>5108.2688</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22923.648</v>
+        <v>22919.3735</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.38</v>
+        <v>32.548</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>249.05</v>
+        <v>245.75</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>46.3</v>
+        <v>46.45</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5108.2688</v>
+        <v>5152.02292</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>22919.3735</v>
+        <v>23105.8252</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.548</v>
+        <v>32.601</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -8126,7 +8126,7 @@
         <v/>
       </c>
       <c r="C3" s="61" t="n">
-        <v>245.75</v>
+        <v>240.75</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="C3" s="128" t="n">
-        <v>46.45</v>
+        <v>46.5</v>
       </c>
       <c r="D3" s="56">
         <f>SUM(D7:D505)</f>
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5152.02292</v>
+        <v>5149.979969999999</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>23105.8252</v>
+        <v>23059.33932</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>

--- a/帳目表.xlsx
+++ b/帳目表.xlsx
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="130" t="n">
-        <v>32.601</v>
+        <v>32.605</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -24705,7 +24705,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>5149.979969999999</v>
+        <v>5064.53465</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
@@ -34615,7 +34615,7 @@
         <v/>
       </c>
       <c r="H3" s="51" t="n">
-        <v>23059.33932</v>
+        <v>22654.28005</v>
       </c>
       <c r="I3" s="140">
         <f>投資!G2</f>
